--- a/public/file/Trax Return Status Template.xlsx
+++ b/public/file/Trax Return Status Template.xlsx
@@ -1,23 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Waqas\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A8B26F-F617-45C8-A335-595EABF98E78}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1440" windowWidth="23040" windowHeight="8496"/>
+    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="12696" xr2:uid="{395B0C63-56F6-410C-8B2D-73DC5C1DC16C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -29,16 +36,16 @@
     <t>Tracking Number</t>
   </si>
   <si>
-    <t>Remarks</t>
+    <t>Status (0 - Confirm / 1 - Re-Attempt)</t>
   </si>
   <si>
-    <t>Status (0 - Confirm / 1 - Re-Attempt)</t>
+    <t>Remarks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -68,9 +75,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -384,49 +390,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07CE767D-B3D7-4239-8AD9-1167FA550765}">
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="34" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/file/Trax Return Status Template.xlsx
+++ b/public/file/Trax Return Status Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Waqas\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trax\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A8B26F-F617-45C8-A335-595EABF98E78}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358A9ABE-51A7-404F-9F16-103E0837DF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="12696" xr2:uid="{395B0C63-56F6-410C-8B2D-73DC5C1DC16C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{395B0C63-56F6-410C-8B2D-73DC5C1DC16C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,25 +31,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Tracking Number</t>
   </si>
   <si>
-    <t>Status (0 - Confirm / 1 - Re-Attempt)</t>
+    <t>Remarks</t>
   </si>
   <si>
-    <t>Remarks</t>
+    <t>Status (0 - Confirm / 1 - Re-Attempt / 2 - NSA)</t>
+  </si>
+  <si>
+    <t>Estimation Charges</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -72,13 +83,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -391,26 +405,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07CE767D-B3D7-4239-8AD9-1167FA550765}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/file/Trax Return Status Template.xlsx
+++ b/public/file/Trax Return Status Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trax\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358A9ABE-51A7-404F-9F16-103E0837DF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA1A1A1-C8AB-45FA-8CE9-50B649B805BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{395B0C63-56F6-410C-8B2D-73DC5C1DC16C}"/>
   </bookViews>
@@ -39,10 +39,10 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>Status (0 - Confirm / 1 - Re-Attempt / 2 - NSA)</t>
+    <t>Estimation Charges</t>
   </si>
   <si>
-    <t>Estimation Charges</t>
+    <t>Status (0 - Confirm / 1 - Re-Attempt / 2 - OSA)</t>
   </si>
 </sst>
 </file>
@@ -419,13 +419,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">

--- a/public/file/Trax Return Status Template.xlsx
+++ b/public/file/Trax Return Status Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trax\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA1A1A1-C8AB-45FA-8CE9-50B649B805BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADB9CFB-BDF0-4E6E-B1B7-1A4D72B6F454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{395B0C63-56F6-410C-8B2D-73DC5C1DC16C}"/>
   </bookViews>
@@ -36,31 +36,23 @@
     <t>Tracking Number</t>
   </si>
   <si>
+    <t>Status (0 - Confirm / 1 - Re-Attempt)</t>
+  </si>
+  <si>
     <t>Remarks</t>
   </si>
   <si>
     <t>Estimation Charges</t>
-  </si>
-  <si>
-    <t>Status (0 - Confirm / 1 - Re-Attempt / 2 - OSA)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -83,16 +75,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -405,13 +394,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07CE767D-B3D7-4239-8AD9-1167FA550765}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -419,20 +407,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>